--- a/4. Supervised Learning (modeling and evaluation)/biases_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer1.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1257729655766236</v>
+        <v>-0.007633588966149499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.08135159362937633</v>
+        <v>0.0620783728900504</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.1753743319800189</v>
+        <v>0.1050079301022322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.2645675320644215</v>
+        <v>0.1227728248934696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.03456528121580332</v>
+        <v>0.01459629209605577</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.149695434008929</v>
+        <v>0.219709669939808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.09360184678136931</v>
+        <v>-0.09432783446561943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.1234656052198465</v>
+        <v>0.148421348008283</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.2107868359479457</v>
+        <v>0.1789525801257217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.2402621143235426</v>
+        <v>-0.05807442703369249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.1135806446512583</v>
+        <v>-0.01863332605385378</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1275218852486115</v>
+        <v>0.1091723656987355</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.008021127271959375</v>
+        <v>-0.1727213240255523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1345117816241178</v>
+        <v>-0.008982357321388612</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.1286515845756969</v>
+        <v>0.05352388522332134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.08361946671381475</v>
+        <v>0.163642859402782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.1634808832409194</v>
+        <v>-0.004594824898230375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.1909624815569593</v>
+        <v>-0.07071340949667314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.05530413736898419</v>
+        <v>0.02029006931603533</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.001365893252077576</v>
+        <v>-0.1476409012243889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.02149425638900099</v>
+        <v>0.1976485882039022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1398482378651246</v>
+        <v>0.1860538525322916</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.03473817816775931</v>
+        <v>0.169092843985355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.04764659200768502</v>
+        <v>0.0004663046204454295</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.1700044787930836</v>
+        <v>-0.192452903651173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.0289406875434913</v>
+        <v>-0.04531260712249327</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.2274299682977385</v>
+        <v>-0.0678755601843424</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.1203019873187425</v>
+        <v>-0.2374881534305065</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.07422556328863648</v>
+        <v>0.0240121724287627</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.03504574331342202</v>
+        <v>-0.03818350031537009</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.05849337991227657</v>
+        <v>0.1293875869555453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.2243639380641208</v>
+        <v>0.03160892541546759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.008557946570614981</v>
+        <v>0.1199821330616585</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.1063076170413558</v>
+        <v>0.0394467979371626</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.1089037299032568</v>
+        <v>0.108310416059212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.0728625154165204</v>
+        <v>-0.2505478749979363</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1119489900923471</v>
+        <v>-0.01629065325890157</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.1654170633987398</v>
+        <v>0.1224875057819338</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.1462432090414129</v>
+        <v>0.1064816515058401</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.1201905069751771</v>
+        <v>0.004092344019802111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.1464179950785324</v>
+        <v>0.01439580441342892</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.2053330356031489</v>
+        <v>-0.1098081787727261</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.1589478594205705</v>
+        <v>-0.1858723406552668</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.1593541297465241</v>
+        <v>-0.1662043339292306</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.0494554180249954</v>
+        <v>-0.09269114341758808</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.03626347349961827</v>
+        <v>0.07843055132033745</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01140225418274875</v>
+        <v>-0.1133450010605263</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.1557743713635253</v>
+        <v>-0.1365586563329026</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.2166096543400088</v>
+        <v>-0.2336768663856275</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.2147111363013524</v>
+        <v>0.01125585736459865</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.09921399351020675</v>
+        <v>0.09055176998901726</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.182749072131887</v>
+        <v>0.1935068980233129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.1193769354827053</v>
+        <v>0.1120890925448154</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.222411020602911</v>
+        <v>-0.01572760530767992</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.009843911568233747</v>
+        <v>0.2223310130538701</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.04322715499536472</v>
+        <v>0.0175063781379837</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.1166018733218115</v>
+        <v>0.206985612008909</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1639737297984822</v>
+        <v>0.07866676537140584</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.1520416975006887</v>
+        <v>-0.1882724121031189</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.1417021711305345</v>
+        <v>0.2359807551958984</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.08037070953673653</v>
+        <v>-0.04753644978754919</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.07743384145143981</v>
+        <v>0.1754216285077303</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.2175488614076149</v>
+        <v>0.1015579973739562</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.1900922929993332</v>
+        <v>0.1039686768420793</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.08357238031739034</v>
+        <v>0.1389703318562293</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.1193186204563718</v>
+        <v>-0.0240577515148922</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.1967190192985813</v>
+        <v>-0.04607597419348183</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.1905609829188177</v>
+        <v>0.192270707510029</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.00857883209890096</v>
+        <v>0.002186867442572415</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.005514622436939736</v>
+        <v>0.1893530136724311</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.1309422122684965</v>
+        <v>-0.01640668830790641</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.04737539005110999</v>
+        <v>0.1278629947468779</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.003823264515710766</v>
+        <v>-0.1142852768489179</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.1903523918881462</v>
+        <v>-0.2303910394827828</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.1766808813529802</v>
+        <v>0.242872234242672</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.2068981075629756</v>
+        <v>-0.09012153791557603</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.1099036624353761</v>
+        <v>0.1717445031290984</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.04038884743492015</v>
+        <v>0.04789619580099014</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.0132111071681556</v>
+        <v>-0.2166176856497826</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.01158329609965709</v>
+        <v>-0.05058062869051706</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.00273733905886201</v>
+        <v>0.107146159845854</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-0.2276151392046625</v>
+        <v>0.1886059437704706</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.009976035959414476</v>
+        <v>0.05181403377758786</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.1845105892975018</v>
+        <v>-0.1000758078368989</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.1982055823722383</v>
+        <v>0.0618846885301137</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.06787876155617123</v>
+        <v>0.03466570460987165</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.04986400287474459</v>
+        <v>0.1353013164969335</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.005669502327274972</v>
+        <v>-0.006581720630233827</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.1140885198934419</v>
+        <v>0.07410805472538086</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.1234120545745035</v>
+        <v>0.1779293893568059</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.02902381783310709</v>
+        <v>-0.04646761572504979</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.09337886582007995</v>
+        <v>-0.1068104778338516</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.1359029676610596</v>
+        <v>-0.1608856190651825</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1081636651968987</v>
+        <v>-0.1873309343809879</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.08973569452394871</v>
+        <v>0.1324293939047951</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.03862342493198664</v>
+        <v>-0.03136430531776602</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-0.05978376817174594</v>
+        <v>-0.1069789686565446</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.1267511756224884</v>
+        <v>-0.2378428073617988</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.1620254173479709</v>
+        <v>0.2002191637984242</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.04586284117910639</v>
+        <v>-0.1493624700275941</v>
       </c>
     </row>
   </sheetData>
